--- a/code/cod_algorithm/z_archived/sample_template.xlsx
+++ b/code/cod_algorithm/z_archived/sample_template.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,11 +362,6 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>MANNER</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>CAUSE</t>
         </is>
       </c>
@@ -377,12 +372,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -390,9 +380,9 @@
       <c r="A3">
         <v>24800</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CANCER OF THE ABDOMIN</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NA: CANCER OF THE ABDOMIN</t>
         </is>
       </c>
     </row>
@@ -402,12 +392,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -417,7 +402,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>NATURAL CAUSES/ILLNESS: NA</t>
         </is>
       </c>
     </row>
@@ -427,7 +412,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accidental Alcohol/drug intoxication (specify type)</t>
+          <t>Accidental Alcohol/drug intoxication (specify type): Methamphetamine Overdose, Unintentional</t>
         </is>
       </c>
     </row>
@@ -440,9 +425,9 @@
       <c r="A8">
         <v>26908</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>cardiac arrest</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NA: cardiac arrest</t>
         </is>
       </c>
     </row>
@@ -452,12 +437,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cardiac Arrest</t>
+          <t>Illness: Cardiac Arrest</t>
         </is>
       </c>
     </row>
@@ -472,12 +452,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -487,12 +462,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>All other illnesses</t>
+          <t>Natural: Heart disease</t>
         </is>
       </c>
     </row>
@@ -502,12 +472,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Acute respiratory failure</t>
+          <t>Illness: Acute respiratory failure</t>
         </is>
       </c>
     </row>
@@ -517,7 +482,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>Natural Cause: NA</t>
         </is>
       </c>
     </row>
@@ -527,12 +492,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Metastatic Testicular Cancer</t>
+          <t>Illness: Metastatic Testicular Cancer</t>
         </is>
       </c>
     </row>
@@ -542,12 +502,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -557,12 +512,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CARDIAC ARREST</t>
+          <t>NATURAL: CARDIAC ARREST</t>
         </is>
       </c>
     </row>
@@ -572,12 +522,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -587,7 +532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NATURAL CAUSE</t>
+          <t>NATURAL CAUSE: NA</t>
         </is>
       </c>
     </row>
@@ -597,12 +542,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Natural causes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bronchopneumonia, End Stage Emphysema</t>
+          <t>Natural causes: Multiple Cerebrovascular Accidents, Cerebrovascular Disease, Hypertension</t>
         </is>
       </c>
     </row>
@@ -612,12 +552,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Natural Causes</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Under Review</t>
+          <t>Natural Causes: Under Review</t>
         </is>
       </c>
     </row>
@@ -627,12 +562,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>RESPIRATORY FAILURE</t>
+          <t>NATURAL CAUSES/ILLNESS: CARDIOMYOPATHY HEART FAILURE</t>
         </is>
       </c>
     </row>
@@ -642,12 +572,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ruptured Ilias Aneurysm</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Aneurysm Ruptured</t>
+          <t>Ruptured Ilias Aneurysm: Aneurysm Ruptured</t>
         </is>
       </c>
     </row>
@@ -657,7 +582,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SUICIDE</t>
+          <t>Suicide: NA</t>
         </is>
       </c>
     </row>
@@ -665,9 +590,9 @@
       <c r="A25">
         <v>34918</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>IDIOPATHIC PULMONARY FIBROSIS</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NA: IDIOPATHIC PULMONARY FIBROSIS</t>
         </is>
       </c>
     </row>
@@ -682,7 +607,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Accidental Alcohol/drug intoxication (specify type)</t>
+          <t>Accidental Alcohol/drug intoxication (specify type): Acute methamphetamine Toxicity</t>
         </is>
       </c>
     </row>
@@ -692,12 +617,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -707,12 +627,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Complications of Lung Cancer w/Sepsis &amp; Acute Respiratory Failure</t>
+          <t>Illness: Complications of Lung Cancer w/Sepsis &amp; Acute Respiratory Failure</t>
         </is>
       </c>
     </row>
@@ -722,12 +637,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>LEUKEMIA</t>
+          <t>Illness: LEUKEMIA</t>
         </is>
       </c>
     </row>
@@ -737,7 +647,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Accident</t>
+          <t>Accident: NA</t>
         </is>
       </c>
     </row>
@@ -747,12 +657,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Metastatic renal cell carcinoma</t>
+          <t>Illness: Metastatic renal cell carcinoma</t>
         </is>
       </c>
     </row>
@@ -760,9 +665,9 @@
       <c r="A33">
         <v>25008</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Cardiomyopathy</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NA: Cardiomyopathy</t>
         </is>
       </c>
     </row>
@@ -777,7 +682,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Natural Causes</t>
+          <t>Natural Causes: NA</t>
         </is>
       </c>
     </row>
@@ -787,12 +692,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Metastatic Adenocarcinoma to Brain</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>INTRACRANIAL BLEED DUE TO METS BRAIN CANCER</t>
+          <t>Metastatic Adenocarcinoma to Brain: INTRACRANIAL BLEED DUE TO METS BRAIN CANCER</t>
         </is>
       </c>
     </row>
@@ -802,12 +702,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Metastic CA Lung</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>cancer lung  w/ mets to brain</t>
+          <t>Metastic CA Lung: cancer lung  w/ mets to brain</t>
         </is>
       </c>
     </row>
@@ -817,7 +712,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Natural Cause</t>
+          <t>Natural Cause: NA</t>
         </is>
       </c>
     </row>
@@ -827,12 +722,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CARDIO PULMONARY ARREST</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Cardiopumonary arrest</t>
+          <t>CARDIO PULMONARY ARREST: Cardiopumonary arrest</t>
         </is>
       </c>
     </row>
@@ -842,12 +732,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Metastatic sigmoid colon cancer</t>
+          <t>Illness: Metastatic sigmoid colon cancer</t>
         </is>
       </c>
     </row>
@@ -857,12 +742,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -872,12 +752,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AUTOIMMUNE HEPATITIS</t>
+          <t>Illness: AUTOIMMUNE HEPATITIS</t>
         </is>
       </c>
     </row>
@@ -887,12 +762,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ACUTE CARDIAC ARRYTHMIA</t>
+          <t>NATURAL CAUSES/ILLNESS: HEMORRHAGE/ HEPATITIS C</t>
         </is>
       </c>
     </row>
@@ -902,12 +772,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>PRELIMINARY - CARDIORESPIRATORY FAILURE/DIABETES</t>
+          <t>NATURAL CAUSES/ILLNESS: PRELIMINARY - HEART FAILURE</t>
         </is>
       </c>
     </row>
@@ -917,7 +782,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other causes, specify causes</t>
+          <t>Other causes, specify causes: Undetermined</t>
         </is>
       </c>
     </row>
@@ -932,7 +797,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Natural Cause</t>
+          <t>Natural Cause: NA</t>
         </is>
       </c>
     </row>
@@ -942,12 +807,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unavailable, investigation pending</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Information received by the IDOC Investigations Unit indicated on January 23, 2024, at approximately 5:10 am, [redacted], informed Housing Unit 5 Correctional Officer [redacted] that [redacted], was unresponsive in his bed. [redacted] called a Code 3 (medical emergency) and, with the assistance of responding security staff, moved [redacted] to the floor and began CPR. Facility nursing staff responded, assessed [redacted], and requested emergency medical services (EMS) be called. [redacted] was transported to Jacksonville Memorial Hospital where [redacted] was pronounced deceased at 6:51 am.</t>
+          <t>Natural causes: 01/26/24, Internal Death of Individual in Custody [redacted]. Presumed natural causes at time of death, documented chronic illness: Cancer.</t>
         </is>
       </c>
     </row>
@@ -957,12 +817,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>HYPERTENSIVE INTRACEREBRAL HEMORRHAGE</t>
+          <t>NATURAL CAUSES/ILLNESS: AD CHOLANGIOCARCIANA</t>
         </is>
       </c>
     </row>
@@ -972,12 +827,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Accidental</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>Accidental: Other</t>
         </is>
       </c>
     </row>
@@ -987,12 +837,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>end of stage liver disease</t>
+          <t>Medical: end of stage liver disease</t>
         </is>
       </c>
     </row>
@@ -1002,12 +847,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Septicemia due to Metastic carcinoma of the breast</t>
+          <t>Illness: Septicemia due to Metastic carcinoma of the breast</t>
         </is>
       </c>
     </row>
@@ -1017,12 +857,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1032,7 +867,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SUICIDE</t>
+          <t>NATURAL CAUSES/ILLNESS: CANCER</t>
         </is>
       </c>
     </row>
@@ -1042,7 +877,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>NATURAL CAUSES/ILLNESS: NA</t>
         </is>
       </c>
     </row>
@@ -1052,12 +887,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Acute Anterior Wall Myocardial Infarction (STEMI)</t>
+          <t>Illness: Acute Anterior Wall Myocardial Infarction (STEMI)</t>
         </is>
       </c>
     </row>
@@ -1067,7 +897,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Natural Cause</t>
+          <t>Natural Cause: NA</t>
         </is>
       </c>
     </row>
@@ -1077,7 +907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Undetermined: NA</t>
         </is>
       </c>
     </row>
@@ -1087,12 +917,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Bilateral Pulmonary Thromboemboli.</t>
+          <t>Illness: Bilateral Pulmonary Thromboemboli.</t>
         </is>
       </c>
     </row>
@@ -1102,7 +927,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>NATURAL CAUSES/ILLNESS: NA</t>
         </is>
       </c>
     </row>
@@ -1112,12 +937,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Natural causes</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On 03/30/2023 at 4:58 am, Registered [redacted] informed this reporting Major  [redacted] of the following incident.  While making rounds in the Stateville healthcare unit Registered Nurse [redacted] noticed Individual in Custody  [redacted] not breathing. Upon assessment of Individual in Custody [redacted] it was discovered that Individual in Custody [redacted] had no pulse, blood pressure, or respirations. No life saving measure was utilized, because Individual in Custody [redacted] had a DNR on file that was signed on 03/22/2023. Dr. [redacted] pronounced Individual in Custody [redacted] decease at 4:55 am. </t>
+          <t>Natural causes: Individual in Custody [redacted] passed away at Good Samaritan Hospital in Mount Vernon, IL on 3/31/2023 @ 2:20 p.m.</t>
         </is>
       </c>
     </row>
@@ -1127,12 +947,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1142,12 +957,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Cardiopulmonary arrest as a result of cardiogenic shock</t>
+          <t>Medical: Cardiopulmonary arrest as a result of cardiogenic shock</t>
         </is>
       </c>
     </row>
@@ -1157,12 +967,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1172,12 +977,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Complications of Congestive heart failure, Atherosclerotic and Hypertensive cardiovascular disease</t>
+          <t>Illness: Complications of Congestive heart failure, Atherosclerotic and Hypertensive cardiovascular disease</t>
         </is>
       </c>
     </row>
@@ -1187,7 +987,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>Suicide: Asphyxiation by hanging</t>
         </is>
       </c>
     </row>
@@ -1197,12 +997,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1007,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Pending: NA</t>
         </is>
       </c>
     </row>
@@ -1220,9 +1015,9 @@
       <c r="A69">
         <v>34372</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAD</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NA: CAD</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1027,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Hepatocellular Cancer</t>
+          <t>Illness: Hepatocellular Cancer</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1037,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Recurrect B Cell Lymphoma, w/Sepsis, C. Difficile Colitis &amp; Acute Renal Failure</t>
+          <t>Illness: Recurrect B Cell Lymphoma, w/Sepsis, C. Difficile Colitis &amp; Acute Renal Failure</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1047,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Metastatic Adenocarcinoma</t>
+          <t>Illness: Metastatic Adenocarcinoma</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1057,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Natural: NA</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1067,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>Suicide: Asphyxiation By Hanging</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1082,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Acute necrotizing bacterial bronchopneumonia with the underlying cause as squamous cell carcinoma...</t>
+          <t>Illness: Acute necrotizing bacterial bronchopneumonia with the underlying cause as squamous cell carcinoma...</t>
         </is>
       </c>
     </row>
@@ -1315,9 +1090,9 @@
       <c r="A77">
         <v>35301</v>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Under Review</t>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NA: Under Review</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1102,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Homicide (all years except 2011 and 2012)</t>
+          <t>Homicide (all years except 2011 and 2012): MULTIPLE STAB WOUNDS (HOMICIDE)</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1112,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Respiratory Arrest</t>
+          <t>Illness: Respiratory Arrest</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1122,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1132,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Metastatic Liver Cancer</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Unsuccessful resuscitation</t>
+          <t>Metastatic Liver Cancer: Unsuccessful resuscitation</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1142,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Complications of end stage liver disease due to hepatitis C</t>
+          <t>Illness: Complications of end stage liver disease due to hepatitis C</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1152,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Cirrhosis</t>
+          <t>Illness: Cirrhosis</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1162,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Undetermined: NA</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1172,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Cardiac Arrest</t>
+          <t>Illness: Cardiac Arrest</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1182,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>COVID-19, RESPIRATORY FAILURE</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Complications of COVID-19 Infection</t>
+          <t>COVID-19, RESPIRATORY FAILURE: Complications of COVID-19 Infection</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1192,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Terminal Cancer</t>
+          <t>Illness: Terminal Cancer</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1202,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1212,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Natural</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
+          <t>Natural: Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1222,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>MYOCARDIAL INFARCTION/HTN/BPH</t>
+          <t>Illness: MYOCARDIAL INFARCTION/HTN/BPH</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1232,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Suicide</t>
+          <t>Suicide: SUICIDE BY HANGING- EXTREME OBESITY</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1242,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>CARDIOPULMONARY ARREST</t>
+          <t>Suicide: NA</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1252,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Natural Causes</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Under Review</t>
+          <t>Natural Causes: Under Review</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1262,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Multiple myeloma</t>
+          <t>Illness: Multiple myeloma</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1272,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Natural: NA</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1282,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Suicide</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Hanging,Strangulation</t>
+          <t>Suicide: Hanging,Strangulation</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1292,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NATURAL: NA</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1302,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Renal failure</t>
+          <t>Illness: Renal failure</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1312,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>ACUTE CARDIORESPIRATORY FAILURE; METASTATIC PROSTATE CARCINOMA</t>
+          <t>Illness: ACUTE CARDIORESPIRATORY FAILURE; METASTATIC PROSTATE CARCINOMA</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1322,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Illness</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Chronic destructive pulmonary disease</t>
+          <t>Illness: Chronic destructive pulmonary disease</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1332,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>CONGESTIVE HEART</t>
+          <t>NATURAL CAUSES/ILLNESS: CONGESTIVE HEART</t>
         </is>
       </c>
     </row>
